--- a/data/trans_camb/P71_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,09; 35,66</t>
+          <t>21,96; 35,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,83; 32,66</t>
+          <t>19,66; 33,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -1,33</t>
+          <t>-10,2; -1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,32; 32,41</t>
+          <t>17,09; 32,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 24,45</t>
+          <t>8,1; 23,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 1,44</t>
+          <t>-11,5; 1,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,35; 31,47</t>
+          <t>21,24; 32,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,57; 26,32</t>
+          <t>16,64; 26,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -1,55</t>
+          <t>-9,54; -1,93</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>151,14; 466,42</t>
+          <t>157,03; 452,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>133,33; 407,68</t>
+          <t>135,32; 410,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,79; -14,39</t>
+          <t>-74,95; -16,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88,89; 295,7</t>
+          <t>91,48; 280,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,99; 204,02</t>
+          <t>38,78; 204,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,88; 20,67</t>
+          <t>-63,25; 14,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>142,51; 303,82</t>
+          <t>133,11; 310,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>109,59; 252,56</t>
+          <t>112,58; 260,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,27; -12,6</t>
+          <t>-62,14; -16,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,41; 35,13</t>
+          <t>23,13; 34,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 21,87</t>
+          <t>9,63; 21,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,54; -6,28</t>
+          <t>-16,87; -5,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,93; 27,05</t>
+          <t>14,18; 26,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 13,15</t>
+          <t>0,49; 12,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,86; -16,44</t>
+          <t>-26,11; -16,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,41; 29,51</t>
+          <t>20,75; 29,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 15,77</t>
+          <t>6,93; 15,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,06; -12,43</t>
+          <t>-20,42; -12,53</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,68; 164,82</t>
+          <t>81,29; 162,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,57; 100,61</t>
+          <t>34,08; 101,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,16; -27,86</t>
+          <t>-63,1; -24,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,68; 85,25</t>
+          <t>37,87; 84,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 42,3</t>
+          <t>1,25; 38,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,74; -51,17</t>
+          <t>-69,46; -51,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,5; 107,52</t>
+          <t>64,57; 108,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,05; 57,05</t>
+          <t>21,46; 56,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,52; -45,46</t>
+          <t>-63,41; -45,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 5,75</t>
+          <t>-6,29; 5,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 14,01</t>
+          <t>1,71; 14,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 5,5</t>
+          <t>-7,11; 4,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -5,38</t>
+          <t>-17,36; -4,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 14,01</t>
+          <t>-0,12; 13,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 0,33</t>
+          <t>-11,91; 0,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -2,0</t>
+          <t>-10,2; -2,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,56</t>
+          <t>2,69; 12,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 0,55</t>
+          <t>-7,59; 0,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 43,45</t>
+          <t>-32,76; 43,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,66; 106,06</t>
+          <t>8,1; 118,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 42,15</t>
+          <t>-36,61; 35,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,52; -22,52</t>
+          <t>-60,34; -23,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 64,33</t>
+          <t>-0,37; 65,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 1,41</t>
+          <t>-40,75; 1,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,13; -10,1</t>
+          <t>-43,68; -10,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,63; 66,05</t>
+          <t>11,14; 64,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 3,05</t>
+          <t>-32,67; 3,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 18,8</t>
+          <t>8,01; 19,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,24; 24,48</t>
+          <t>12,1; 24,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 4,45</t>
+          <t>-6,35; 3,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 9,59</t>
+          <t>-3,36; 8,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 22,07</t>
+          <t>8,98; 22,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 35,38</t>
+          <t>-4,89; 38,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,36; 11,69</t>
+          <t>3,86; 12,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 21,61</t>
+          <t>12,59; 21,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 28,32</t>
+          <t>-3,15; 29,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>50,16; 194,22</t>
+          <t>55,12; 206,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,79; 252,53</t>
+          <t>80,58; 259,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 46,77</t>
+          <t>-45,59; 40,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 48,01</t>
+          <t>-13,21; 45,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,24; 110,61</t>
+          <t>33,73; 116,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 183,87</t>
+          <t>-20,85; 180,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,86; 73,79</t>
+          <t>19,46; 78,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>62,59; 138,06</t>
+          <t>63,33; 136,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 169,11</t>
+          <t>-17,21; 178,82</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,28; 27,5</t>
+          <t>10,72; 26,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37,88; 54,48</t>
+          <t>38,19; 54,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,52; -4,48</t>
+          <t>-15,94; -4,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,25; 23,97</t>
+          <t>5,42; 23,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36,34; 52,98</t>
+          <t>37,02; 53,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,82; -10,17</t>
+          <t>-22,7; -9,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,53; 22,68</t>
+          <t>10,94; 23,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39,74; 51,16</t>
+          <t>38,95; 51,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,87; -9,02</t>
+          <t>-18,09; -8,87</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>62,3; 245,14</t>
+          <t>57,71; 242,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>206,13; 487,71</t>
+          <t>190,0; 479,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,35; -35,76</t>
+          <t>-81,64; -29,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18,24; 139,89</t>
+          <t>20,91; 134,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>134,37; 326,65</t>
+          <t>138,87; 338,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,47; -60,01</t>
+          <t>-88,3; -56,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,66; 147,48</t>
+          <t>51,35; 154,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>184,94; 341,02</t>
+          <t>181,88; 354,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,38; -57,63</t>
+          <t>-83,67; -57,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 2,16</t>
+          <t>-10,44; 2,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 4,83</t>
+          <t>-8,76; 4,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,95; -2,83</t>
+          <t>-14,45; -2,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-24,0; -9,66</t>
+          <t>-23,71; -9,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,41; -5,56</t>
+          <t>-20,92; -5,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-23,2; -9,7</t>
+          <t>-23,06; -10,15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -5,14</t>
+          <t>-15,53; -6,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -2,91</t>
+          <t>-13,02; -2,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,87; -8,43</t>
+          <t>-17,69; -8,08</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 12,85</t>
+          <t>-45,05; 14,7</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-35,62; 30,11</t>
+          <t>-35,69; 26,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,96; -15,08</t>
+          <t>-60,23; -14,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-65,9; -33,34</t>
+          <t>-65,97; -33,8</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-57,79; -20,54</t>
+          <t>-58,62; -20,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-64,37; -34,47</t>
+          <t>-65,01; -36,97</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-52,88; -20,85</t>
+          <t>-53,63; -25,29</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,46; -12,4</t>
+          <t>-45,3; -12,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-60,17; -34,19</t>
+          <t>-60,03; -35,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,68</t>
+          <t>-3,62; 6,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,53; 15,44</t>
+          <t>4,88; 15,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,62; -3,47</t>
+          <t>-12,33; -2,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-16,28; -5,97</t>
+          <t>-15,59; -5,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 3,96</t>
+          <t>-6,79; 3,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-32,64; -18,79</t>
+          <t>-32,67; -18,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -1,67</t>
+          <t>-8,25; -1,1</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 7,91</t>
+          <t>0,66; 8,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-21,31; -12,62</t>
+          <t>-20,94; -12,65</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 32,26</t>
+          <t>-15,85; 37,81</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>23,19; 86,05</t>
+          <t>20,94; 85,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,31; -18,68</t>
+          <t>-54,57; -14,96</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-43,22; -18,59</t>
+          <t>-42,45; -16,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 12,74</t>
+          <t>-17,94; 10,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-83,44; -56,27</t>
+          <t>-85,56; -56,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-30,48; -6,35</t>
+          <t>-27,93; -4,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,89; 30,27</t>
+          <t>2,41; 32,92</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-74,33; -48,47</t>
+          <t>-73,72; -48,1</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>9,68; 18,69</t>
+          <t>10,08; 19,12</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10,15; 19,27</t>
+          <t>10,12; 18,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 3,17</t>
+          <t>-13,37; 3,31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4,3; 13,61</t>
+          <t>3,86; 13,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,12</t>
+          <t>2,59; 11,83</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 1,28</t>
+          <t>-8,06; 0,9</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,41; 14,78</t>
+          <t>8,51; 15,02</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,41; 13,98</t>
+          <t>7,46; 13,82</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 0,26</t>
+          <t>-11,49; 0,41</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>45,57; 114,74</t>
+          <t>46,83; 113,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>47,97; 117,55</t>
+          <t>48,84; 114,71</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,2; 17,71</t>
+          <t>-64,92; 19,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15,03; 58,58</t>
+          <t>13,9; 58,19</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,55; 50,99</t>
+          <t>9,09; 50,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 6,04</t>
+          <t>-28,14; 4,02</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,25; 71,95</t>
+          <t>35,7; 71,74</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>31,23; 68,46</t>
+          <t>30,95; 66,8</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-47,56; 1,02</t>
+          <t>-52,01; 1,82</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>10,51; 14,59</t>
+          <t>10,64; 14,75</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>13,3; 17,53</t>
+          <t>13,32; 17,71</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -4,04</t>
+          <t>-9,08; -3,95</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,09</t>
+          <t>1,56; 6,01</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,37</t>
+          <t>5,45; 10,23</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,21; -5,86</t>
+          <t>-14,3; -5,85</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,65</t>
+          <t>6,5; 9,7</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>9,91; 13,22</t>
+          <t>10,18; 13,31</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -5,45</t>
+          <t>-10,79; -5,63</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>54,41; 84,54</t>
+          <t>55,83; 85,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>69,88; 103,67</t>
+          <t>70,34; 103,99</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-47,77; -23,5</t>
+          <t>-49,51; -23,2</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5,04; 22,74</t>
+          <t>5,5; 22,88</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>20,02; 38,58</t>
+          <t>18,72; 38,62</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-49,98; -21,82</t>
+          <t>-50,14; -21,34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>27,03; 43,52</t>
+          <t>27,29; 43,99</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>41,19; 59,59</t>
+          <t>42,53; 60,45</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-44,86; -23,19</t>
+          <t>-45,3; -24,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P71_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-5,58</t>
+          <t>-3,15</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,62</t>
+          <t>-5,31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,62</t>
+          <t>-4,18</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,96; 35,99</t>
+          <t>21,43; 35,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,66; 33,21</t>
+          <t>19,43; 33,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,2; -1,5</t>
+          <t>-7,89; 1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,09; 32,95</t>
+          <t>17,05; 32,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 23,58</t>
+          <t>9,62; 23,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 1,18</t>
+          <t>-11,25; -0,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,24; 32,39</t>
+          <t>21,93; 32,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 26,48</t>
+          <t>16,22; 26,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -1,93</t>
+          <t>-7,72; -0,62</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-52,53%</t>
+          <t>-29,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-37,75%</t>
+          <t>-35,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-44,25%</t>
+          <t>-32,92%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>157,03; 452,64</t>
+          <t>151,03; 469,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>135,32; 410,87</t>
+          <t>142,56; 433,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,95; -16,49</t>
+          <t>-57,66; 20,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91,48; 280,85</t>
+          <t>88,55; 283,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,78; 204,51</t>
+          <t>53,12; 195,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 14,91</t>
+          <t>-59,42; -0,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>133,11; 310,19</t>
+          <t>141,96; 318,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>112,58; 260,22</t>
+          <t>107,55; 255,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,14; -16,07</t>
+          <t>-51,74; -4,61</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-11,7</t>
+          <t>-11,76</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-21,37</t>
+          <t>-21,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-16,56</t>
+          <t>-16,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,13; 34,92</t>
+          <t>22,85; 34,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,63; 21,79</t>
+          <t>10,12; 22,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -5,55</t>
+          <t>-16,97; -5,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,18; 26,83</t>
+          <t>14,25; 27,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 12,3</t>
+          <t>1,02; 12,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,11; -16,57</t>
+          <t>-26,48; -16,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,75; 29,7</t>
+          <t>20,07; 29,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 15,71</t>
+          <t>6,9; 15,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,42; -12,53</t>
+          <t>-20,17; -12,76</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-47,54%</t>
+          <t>-47,79%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-60,9%</t>
+          <t>-60,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-55,43%</t>
+          <t>-55,06%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,29; 162,42</t>
+          <t>84,38; 163,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,08; 101,01</t>
+          <t>37,45; 102,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,1; -24,2</t>
+          <t>-62,43; -26,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,87; 84,62</t>
+          <t>37,56; 84,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 38,22</t>
+          <t>2,91; 42,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,46; -51,06</t>
+          <t>-69,03; -50,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,57; 108,76</t>
+          <t>62,36; 105,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,46; 56,52</t>
+          <t>21,77; 55,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,41; -45,16</t>
+          <t>-62,63; -45,58</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,97</t>
+          <t>-5,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,57</t>
+          <t>-2,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 5,69</t>
+          <t>-6,5; 5,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 14,82</t>
+          <t>1,66; 14,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 4,63</t>
+          <t>-6,09; 6,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -4,57</t>
+          <t>-17,51; -4,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 13,96</t>
+          <t>-0,53; 13,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 0,37</t>
+          <t>-11,4; 1,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,2; -2,14</t>
+          <t>-10,12; -1,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,13</t>
+          <t>2,65; 12,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 0,53</t>
+          <t>-6,85; 1,99</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-7,12%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-23,37%</t>
+          <t>-19,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,02%</t>
+          <t>-11,89%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,76; 43,53</t>
+          <t>-34,21; 41,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,1; 118,22</t>
+          <t>7,73; 110,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 35,42</t>
+          <t>-31,78; 46,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,34; -23,1</t>
+          <t>-59,96; -22,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 65,17</t>
+          <t>-1,82; 63,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,75; 1,79</t>
+          <t>-39,57; 5,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,68; -10,79</t>
+          <t>-42,86; -7,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,14; 64,27</t>
+          <t>11,57; 66,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 3,44</t>
+          <t>-28,64; 10,45</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,19</t>
+          <t>-0,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,01; 19,61</t>
+          <t>7,81; 19,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,1; 24,79</t>
+          <t>12,0; 24,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 3,83</t>
+          <t>-4,27; 8,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 8,92</t>
+          <t>-3,45; 8,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,98; 22,48</t>
+          <t>9,09; 22,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 38,14</t>
+          <t>-8,21; 3,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 12,7</t>
+          <t>3,87; 12,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,59; 21,6</t>
+          <t>12,51; 21,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 29,08</t>
+          <t>-4,64; 3,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-11,46%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>-11,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>-1,75%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>55,12; 206,71</t>
+          <t>56,01; 203,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,58; 259,03</t>
+          <t>80,59; 254,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 40,83</t>
+          <t>-30,41; 78,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 45,01</t>
+          <t>-13,42; 45,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,73; 116,2</t>
+          <t>36,18; 114,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 180,62</t>
+          <t>-31,73; 15,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,46; 78,91</t>
+          <t>19,29; 78,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>63,33; 136,96</t>
+          <t>64,01; 137,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 178,82</t>
+          <t>-23,95; 23,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,77</t>
+          <t>-7,42</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-16,05</t>
+          <t>-13,89</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-12,93</t>
+          <t>-10,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,72; 26,93</t>
+          <t>10,85; 28,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38,19; 54,0</t>
+          <t>38,43; 55,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -4,57</t>
+          <t>-12,94; -1,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,42; 23,3</t>
+          <t>6,38; 23,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,02; 53,78</t>
+          <t>36,69; 53,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,7; -9,04</t>
+          <t>-20,37; -7,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,94; 23,4</t>
+          <t>10,61; 22,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38,95; 51,27</t>
+          <t>39,55; 52,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -8,87</t>
+          <t>-15,09; -6,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-65,77%</t>
+          <t>-49,98%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-76,07%</t>
+          <t>-65,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-71,85%</t>
+          <t>-59,32%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>57,71; 242,41</t>
+          <t>53,26; 255,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>190,0; 479,14</t>
+          <t>201,92; 532,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,64; -29,81</t>
+          <t>-72,79; -4,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,91; 134,21</t>
+          <t>24,82; 145,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>138,87; 338,89</t>
+          <t>141,94; 340,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,3; -56,47</t>
+          <t>-78,86; -45,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,35; 154,58</t>
+          <t>49,88; 153,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>181,88; 354,27</t>
+          <t>176,65; 345,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,67; -57,16</t>
+          <t>-71,77; -41,56</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-8,58</t>
+          <t>-6,92</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-16,99</t>
+          <t>-16,15</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-12,88</t>
+          <t>-11,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 2,54</t>
+          <t>-10,26; 2,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 4,68</t>
+          <t>-9,5; 5,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,45; -2,81</t>
+          <t>-13,07; -0,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-23,71; -9,68</t>
+          <t>-23,84; -9,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,92; -5,97</t>
+          <t>-20,72; -6,23</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-23,06; -10,15</t>
+          <t>-22,65; -9,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-15,53; -6,07</t>
+          <t>-15,22; -5,77</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,02; -2,81</t>
+          <t>-13,09; -2,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,69; -8,08</t>
+          <t>-15,94; -7,02</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-41,88%</t>
+          <t>-33,82%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-52,75%</t>
+          <t>-50,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-48,79%</t>
+          <t>-43,99%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-45,05; 14,7</t>
+          <t>-44,1; 16,14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 26,6</t>
+          <t>-38,77; 29,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-60,23; -14,17</t>
+          <t>-54,95; -3,37</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-65,97; -33,8</t>
+          <t>-66,54; -32,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-58,62; -20,95</t>
+          <t>-58,25; -21,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-65,01; -36,97</t>
+          <t>-62,07; -34,51</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-53,63; -25,29</t>
+          <t>-52,56; -23,38</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-45,3; -12,2</t>
+          <t>-44,6; -10,73</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-60,03; -35,1</t>
+          <t>-54,43; -29,91</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-7,86</t>
+          <t>-8,14</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-23,86</t>
+          <t>-19,88</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-16,12</t>
+          <t>-14,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 6,48</t>
+          <t>-4,0; 6,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,88; 15,19</t>
+          <t>4,84; 15,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -2,64</t>
+          <t>-12,94; -4,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-15,59; -5,19</t>
+          <t>-15,54; -5,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 3,7</t>
+          <t>-6,36; 4,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-32,67; -18,76</t>
+          <t>-24,37; -15,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -1,1</t>
+          <t>-8,71; -1,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,4</t>
+          <t>0,41; 7,91</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-20,94; -12,65</t>
+          <t>-17,04; -10,62</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-38,87%</t>
+          <t>-40,21%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-69,05%</t>
+          <t>-57,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-58,58%</t>
+          <t>-51,2%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 37,81</t>
+          <t>-17,99; 33,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20,94; 85,29</t>
+          <t>21,32; 88,88</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,57; -14,96</t>
+          <t>-54,85; -19,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,45; -16,65</t>
+          <t>-41,57; -17,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 10,58</t>
+          <t>-16,81; 13,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-85,56; -56,84</t>
+          <t>-65,05; -49,13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-27,93; -4,03</t>
+          <t>-29,13; -5,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,41; 32,92</t>
+          <t>1,67; 31,01</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-73,72; -48,1</t>
+          <t>-58,3; -41,67</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,66</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-3,1</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10,08; 19,12</t>
+          <t>10,04; 19,2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10,12; 18,69</t>
+          <t>10,21; 19,22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 3,31</t>
+          <t>-0,77; 7,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,86; 13,39</t>
+          <t>4,01; 13,37</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,83</t>
+          <t>2,38; 11,85</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 0,9</t>
+          <t>-6,81; 1,79</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,02</t>
+          <t>8,51; 15,09</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,46; 13,82</t>
+          <t>7,58; 14,05</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 0,41</t>
+          <t>-2,72; 3,26</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-19,8%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-12,16%</t>
+          <t>-9,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-17,9%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>46,83; 113,37</t>
+          <t>49,18; 116,11</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>48,84; 114,71</t>
+          <t>48,71; 116,26</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,92; 19,01</t>
+          <t>-3,84; 47,46</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13,9; 58,19</t>
+          <t>14,03; 57,73</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,09; 50,41</t>
+          <t>8,35; 51,31</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 4,02</t>
+          <t>-24,09; 7,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,7; 71,74</t>
+          <t>34,92; 74,27</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>30,95; 66,8</t>
+          <t>32,03; 69,09</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-52,01; 1,82</t>
+          <t>-11,43; 16,21</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-5,95</t>
+          <t>-3,75</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-11,15</t>
+          <t>-10,96</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-8,54</t>
+          <t>-7,38</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>10,64; 14,75</t>
+          <t>10,5; 14,8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>13,32; 17,71</t>
+          <t>13,03; 17,53</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-9,08; -3,95</t>
+          <t>-5,71; -1,95</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,01</t>
+          <t>1,62; 6,09</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,23</t>
+          <t>5,67; 10,15</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,3; -5,85</t>
+          <t>-12,89; -9,03</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,5; 9,7</t>
+          <t>6,64; 9,61</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>10,18; 13,31</t>
+          <t>9,96; 13,08</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -5,63</t>
+          <t>-8,89; -5,98</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-32,9%</t>
+          <t>-20,76%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-40,07%</t>
+          <t>-39,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-37,1%</t>
+          <t>-32,07%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>55,83; 85,44</t>
+          <t>54,05; 86,69</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>70,34; 103,99</t>
+          <t>68,16; 103,49</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -23,2</t>
+          <t>-30,19; -11,31</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5,5; 22,88</t>
+          <t>5,37; 22,54</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>18,72; 38,62</t>
+          <t>19,59; 37,85</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-50,14; -21,34</t>
+          <t>-44,76; -33,65</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>27,29; 43,99</t>
+          <t>27,52; 42,98</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>42,53; 60,45</t>
+          <t>41,99; 58,88</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-45,3; -24,3</t>
+          <t>-37,09; -26,92</t>
         </is>
       </c>
     </row>
